--- a/docs/AI-Usage/AI Usage Register/AI Usage Register v0.15.xlsx
+++ b/docs/AI-Usage/AI Usage Register/AI Usage Register v0.15.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\elind\m4-wt\records\docs\AI-Usage\AI Usage Register\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{449D37F1-7018-456A-B4A6-1AD814667C38}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7746990F-0A8D-440F-9984-5274705A429E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="30936" windowHeight="17496" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-96" yWindow="-96" windowWidth="30912" windowHeight="17472" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="AI Usage Register" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="639" uniqueCount="451">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="653" uniqueCount="461">
   <si>
     <t>AI Usage Register</t>
   </si>
@@ -1488,6 +1488,36 @@
   </si>
   <si>
     <t>The AI’s drafts needed 14 corrections before use, mostly figures and statuses that had changed since they were written; nothing was carried into PED v4.0 without being checked against the registers.</t>
+  </si>
+  <si>
+    <t>TD-008: run the 8 integration cases in CI</t>
+  </si>
+  <si>
+    <t>Drafted a sixth CI job that starts a single-node MongoDB 8.0 replica set on the runner, with no cluster credential, and runs the cases against it; the harness change that accepts that loopback host only when CI=true; and a step that fails the job if the cases were skipped. Wrote the expected result before the run: 40 tests, 25 pass, 15 fail (DEF-007 to DEF-011)</t>
+  </si>
+  <si>
+    <t>The run on PR #122 matched the prediction exactly: 40 tests, 25 pass, 15 fail, 0 skipped. Before that, the full suite with the harness change was unchanged from dev (199 tests, 191 pass), the host rule was tested against four URIs, and the skip guard failed the step when no database was given. After PR #136 the same job passed 40/40 on dev (run 39079571516)</t>
+  </si>
+  <si>
+    <t>Accepted with changes. Added as a non-required check while DEF-007 to DEF-011 still failed, so the known failures did not block other merges. After it passed 40/40 on dev, I made it a required check in the dev rule ruleset on 18/10/2026, which repays TD-008</t>
+  </si>
+  <si>
+    <t>TD Register v0.3 planned the known failures as expected failures. node:test has no expected-failure mode that fails when the test starts passing, so I made the job non-required instead of changing any assertion. MongoDB could not be downloaded in the drafting environment, so the replica set was first tried in CI itself</t>
+  </si>
+  <si>
+    <t>Pre-RC fixes : TD-007 OpenAPI tests parse the YAML, DEF-019 test titles, scripts README, .gitignore</t>
+  </si>
+  <si>
+    <t>Rewrote the two OpenAPI contract tests to parse the file with the yaml package as a dev dependency, and added a test for valid YAML, OpenAPI 3.x and resolving references. Corrected the two DEF-019 titles, the stale staging-marker line in the scripts README, and added ignores for the perf fixture file and staging.crt</t>
+  </si>
+  <si>
+    <t>Broke openapi.yaml four ways with the expected results written first: the old tests passed on three of the four, the new ones failed on all four, and the file was restored and hash-checked each time. Full suite 200 tests, 192 pass; ESLint clean; production audit 0 vulnerabilities; the lockfile change is only the yaml package; the ignore rules were tested in an empty repo</t>
+  </si>
+  <si>
+    <t>Accepted. A YAML parser rather than a full OpenAPI validator, with the limit stated in the test headers. Split into three commits, one per fix</t>
+  </si>
+  <si>
+    <t>The negative verification ran in a scratch copy, not in my checkout, and the evidence file says so. One commit message was joined to old text by mistake and was amended before review</t>
   </si>
 </sst>
 </file>
@@ -1657,7 +1687,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="22">
+  <cellXfs count="21">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -1718,9 +1748,6 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -4203,401 +4230,435 @@
     </row>
     <row r="83" spans="2:9" ht="115.2">
       <c r="B83" s="15">
+        <f t="shared" ref="B83:B96" si="3">DATE(2026,10,17)</f>
+        <v>46312</v>
+      </c>
+      <c r="C83" s="5" t="s">
+        <v>326</v>
+      </c>
+      <c r="D83" s="7" t="s">
+        <v>10</v>
+      </c>
+      <c r="E83" s="5" t="s">
+        <v>381</v>
+      </c>
+      <c r="F83" s="5" t="s">
+        <v>402</v>
+      </c>
+      <c r="G83" s="5" t="s">
+        <v>382</v>
+      </c>
+      <c r="H83" s="5" t="s">
+        <v>383</v>
+      </c>
+      <c r="I83" s="5" t="s">
+        <v>384</v>
+      </c>
+    </row>
+    <row r="84" spans="2:9" ht="72">
+      <c r="B84" s="15">
+        <f t="shared" si="3"/>
+        <v>46312</v>
+      </c>
+      <c r="C84" s="5" t="s">
+        <v>326</v>
+      </c>
+      <c r="D84" s="7" t="s">
+        <v>10</v>
+      </c>
+      <c r="E84" s="5" t="s">
+        <v>385</v>
+      </c>
+      <c r="F84" s="5" t="s">
+        <v>386</v>
+      </c>
+      <c r="G84" s="5" t="s">
+        <v>387</v>
+      </c>
+      <c r="H84" s="5" t="s">
+        <v>388</v>
+      </c>
+      <c r="I84" s="5" t="s">
+        <v>389</v>
+      </c>
+    </row>
+    <row r="85" spans="2:9" ht="100.8">
+      <c r="B85" s="15">
+        <f t="shared" si="3"/>
+        <v>46312</v>
+      </c>
+      <c r="C85" s="5" t="s">
+        <v>326</v>
+      </c>
+      <c r="D85" s="7" t="s">
+        <v>10</v>
+      </c>
+      <c r="E85" s="5" t="s">
+        <v>390</v>
+      </c>
+      <c r="F85" s="5" t="s">
+        <v>391</v>
+      </c>
+      <c r="G85" s="5" t="s">
+        <v>392</v>
+      </c>
+      <c r="H85" s="5" t="s">
+        <v>448</v>
+      </c>
+      <c r="I85" s="5" t="s">
+        <v>393</v>
+      </c>
+    </row>
+    <row r="86" spans="2:9" ht="86.4">
+      <c r="B86" s="15">
+        <f t="shared" si="3"/>
+        <v>46312</v>
+      </c>
+      <c r="C86" s="5" t="s">
+        <v>326</v>
+      </c>
+      <c r="D86" s="7" t="s">
+        <v>10</v>
+      </c>
+      <c r="E86" s="5" t="s">
+        <v>394</v>
+      </c>
+      <c r="F86" s="5" t="s">
+        <v>395</v>
+      </c>
+      <c r="G86" s="5" t="s">
+        <v>396</v>
+      </c>
+      <c r="H86" s="5" t="s">
+        <v>397</v>
+      </c>
+      <c r="I86" s="5" t="s">
+        <v>398</v>
+      </c>
+    </row>
+    <row r="87" spans="2:9" ht="86.4">
+      <c r="B87" s="15">
+        <f t="shared" si="3"/>
+        <v>46312</v>
+      </c>
+      <c r="C87" s="5" t="s">
+        <v>326</v>
+      </c>
+      <c r="D87" s="7" t="s">
+        <v>10</v>
+      </c>
+      <c r="E87" s="5" t="s">
+        <v>399</v>
+      </c>
+      <c r="F87" s="5" t="s">
+        <v>400</v>
+      </c>
+      <c r="G87" s="5" t="s">
+        <v>401</v>
+      </c>
+      <c r="H87" s="5" t="s">
+        <v>449</v>
+      </c>
+      <c r="I87" s="5" t="s">
+        <v>450</v>
+      </c>
+    </row>
+    <row r="88" spans="2:9" ht="72">
+      <c r="B88" s="15">
+        <f t="shared" si="3"/>
+        <v>46312</v>
+      </c>
+      <c r="C88" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="D88" s="7" t="s">
+        <v>10</v>
+      </c>
+      <c r="E88" s="5" t="s">
+        <v>403</v>
+      </c>
+      <c r="F88" s="5" t="s">
+        <v>404</v>
+      </c>
+      <c r="G88" s="5" t="s">
+        <v>405</v>
+      </c>
+      <c r="H88" s="5" t="s">
+        <v>406</v>
+      </c>
+      <c r="I88" s="5" t="s">
+        <v>407</v>
+      </c>
+    </row>
+    <row r="89" spans="2:9" ht="86.4">
+      <c r="B89" s="15">
+        <f t="shared" si="3"/>
+        <v>46312</v>
+      </c>
+      <c r="C89" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="D89" s="7" t="s">
+        <v>10</v>
+      </c>
+      <c r="E89" s="5" t="s">
+        <v>408</v>
+      </c>
+      <c r="F89" s="5" t="s">
+        <v>409</v>
+      </c>
+      <c r="G89" s="5" t="s">
+        <v>410</v>
+      </c>
+      <c r="H89" s="5" t="s">
+        <v>411</v>
+      </c>
+      <c r="I89" s="5" t="s">
+        <v>412</v>
+      </c>
+    </row>
+    <row r="90" spans="2:9" ht="115.2">
+      <c r="B90" s="15">
+        <f t="shared" si="3"/>
+        <v>46312</v>
+      </c>
+      <c r="C90" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="D90" s="7" t="s">
+        <v>10</v>
+      </c>
+      <c r="E90" s="5" t="s">
+        <v>413</v>
+      </c>
+      <c r="F90" s="5" t="s">
+        <v>414</v>
+      </c>
+      <c r="G90" s="5" t="s">
+        <v>415</v>
+      </c>
+      <c r="H90" s="5" t="s">
+        <v>416</v>
+      </c>
+      <c r="I90" s="5" t="s">
+        <v>417</v>
+      </c>
+    </row>
+    <row r="91" spans="2:9" ht="115.2">
+      <c r="B91" s="15">
+        <f t="shared" si="3"/>
+        <v>46312</v>
+      </c>
+      <c r="C91" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="D91" s="7" t="s">
+        <v>10</v>
+      </c>
+      <c r="E91" s="5" t="s">
+        <v>418</v>
+      </c>
+      <c r="F91" s="5" t="s">
+        <v>419</v>
+      </c>
+      <c r="G91" s="5" t="s">
+        <v>420</v>
+      </c>
+      <c r="H91" s="5" t="s">
+        <v>421</v>
+      </c>
+      <c r="I91" s="5" t="s">
+        <v>422</v>
+      </c>
+    </row>
+    <row r="92" spans="2:9" ht="100.8">
+      <c r="B92" s="15">
+        <f t="shared" si="3"/>
+        <v>46312</v>
+      </c>
+      <c r="C92" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="D92" s="7" t="s">
+        <v>10</v>
+      </c>
+      <c r="E92" s="5" t="s">
+        <v>423</v>
+      </c>
+      <c r="F92" s="5" t="s">
+        <v>424</v>
+      </c>
+      <c r="G92" s="5" t="s">
+        <v>425</v>
+      </c>
+      <c r="H92" s="5" t="s">
+        <v>426</v>
+      </c>
+      <c r="I92" s="5" t="s">
+        <v>427</v>
+      </c>
+    </row>
+    <row r="93" spans="2:9" ht="86.4">
+      <c r="B93" s="15">
+        <f t="shared" si="3"/>
+        <v>46312</v>
+      </c>
+      <c r="C93" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="D93" s="7" t="s">
+        <v>10</v>
+      </c>
+      <c r="E93" s="5" t="s">
+        <v>428</v>
+      </c>
+      <c r="F93" s="5" t="s">
+        <v>429</v>
+      </c>
+      <c r="G93" s="5" t="s">
+        <v>430</v>
+      </c>
+      <c r="H93" s="5" t="s">
+        <v>431</v>
+      </c>
+      <c r="I93" s="5" t="s">
+        <v>432</v>
+      </c>
+    </row>
+    <row r="94" spans="2:9" ht="43.2">
+      <c r="B94" s="15">
+        <f t="shared" si="3"/>
+        <v>46312</v>
+      </c>
+      <c r="C94" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="D94" s="7" t="s">
+        <v>10</v>
+      </c>
+      <c r="E94" s="5" t="s">
+        <v>433</v>
+      </c>
+      <c r="F94" s="5" t="s">
+        <v>434</v>
+      </c>
+      <c r="G94" s="5" t="s">
+        <v>435</v>
+      </c>
+      <c r="H94" s="5" t="s">
+        <v>436</v>
+      </c>
+      <c r="I94" s="5" t="s">
+        <v>437</v>
+      </c>
+    </row>
+    <row r="95" spans="2:9" ht="72">
+      <c r="B95" s="15">
+        <f t="shared" si="3"/>
+        <v>46312</v>
+      </c>
+      <c r="C95" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="D95" s="7" t="s">
+        <v>10</v>
+      </c>
+      <c r="E95" s="5" t="s">
+        <v>438</v>
+      </c>
+      <c r="F95" s="5" t="s">
+        <v>439</v>
+      </c>
+      <c r="G95" s="5" t="s">
+        <v>440</v>
+      </c>
+      <c r="H95" s="5" t="s">
+        <v>441</v>
+      </c>
+      <c r="I95" s="5" t="s">
+        <v>442</v>
+      </c>
+    </row>
+    <row r="96" spans="2:9" ht="144">
+      <c r="B96" s="15">
+        <f t="shared" si="3"/>
+        <v>46312</v>
+      </c>
+      <c r="C96" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="D96" s="7" t="s">
+        <v>10</v>
+      </c>
+      <c r="E96" s="5" t="s">
+        <v>443</v>
+      </c>
+      <c r="F96" s="5" t="s">
+        <v>444</v>
+      </c>
+      <c r="G96" s="5" t="s">
+        <v>445</v>
+      </c>
+      <c r="H96" s="5" t="s">
+        <v>446</v>
+      </c>
+      <c r="I96" s="5" t="s">
+        <v>447</v>
+      </c>
+    </row>
+    <row r="97" spans="2:9" ht="115.2">
+      <c r="B97" s="15">
         <f>DATE(2026,10,17)</f>
         <v>46312</v>
       </c>
-      <c r="C83" s="5" t="s">
-        <v>326</v>
-      </c>
-      <c r="D83" s="7" t="s">
-        <v>10</v>
-      </c>
-      <c r="E83" s="5" t="s">
-        <v>381</v>
-      </c>
-      <c r="F83" s="21" t="s">
-        <v>402</v>
-      </c>
-      <c r="G83" s="5" t="s">
-        <v>382</v>
-      </c>
-      <c r="H83" s="5" t="s">
-        <v>383</v>
-      </c>
-      <c r="I83" s="5" t="s">
-        <v>384</v>
-      </c>
-    </row>
-    <row r="84" spans="2:9" ht="72">
-      <c r="B84" s="15">
+      <c r="C97" s="5" t="s">
+        <v>67</v>
+      </c>
+      <c r="D97" s="7" t="s">
+        <v>10</v>
+      </c>
+      <c r="E97" s="5" t="s">
+        <v>451</v>
+      </c>
+      <c r="F97" s="5" t="s">
+        <v>452</v>
+      </c>
+      <c r="G97" s="5" t="s">
+        <v>453</v>
+      </c>
+      <c r="H97" s="5" t="s">
+        <v>454</v>
+      </c>
+      <c r="I97" s="5" t="s">
+        <v>455</v>
+      </c>
+    </row>
+    <row r="98" spans="2:9" ht="115.2">
+      <c r="B98" s="15">
         <f>DATE(2026,10,17)</f>
         <v>46312</v>
       </c>
-      <c r="C84" s="5" t="s">
-        <v>326</v>
-      </c>
-      <c r="D84" s="7" t="s">
-        <v>10</v>
-      </c>
-      <c r="E84" s="5" t="s">
-        <v>385</v>
-      </c>
-      <c r="F84" s="5" t="s">
-        <v>386</v>
-      </c>
-      <c r="G84" s="5" t="s">
-        <v>387</v>
-      </c>
-      <c r="H84" s="5" t="s">
-        <v>388</v>
-      </c>
-      <c r="I84" s="5" t="s">
-        <v>389</v>
-      </c>
-    </row>
-    <row r="85" spans="2:9" ht="100.8">
-      <c r="B85" s="15">
-        <f>DATE(2026,10,17)</f>
-        <v>46312</v>
-      </c>
-      <c r="C85" s="5" t="s">
-        <v>326</v>
-      </c>
-      <c r="D85" s="7" t="s">
-        <v>10</v>
-      </c>
-      <c r="E85" s="5" t="s">
-        <v>390</v>
-      </c>
-      <c r="F85" s="5" t="s">
-        <v>391</v>
-      </c>
-      <c r="G85" s="5" t="s">
-        <v>392</v>
-      </c>
-      <c r="H85" s="21" t="s">
-        <v>448</v>
-      </c>
-      <c r="I85" s="5" t="s">
-        <v>393</v>
-      </c>
-    </row>
-    <row r="86" spans="2:9" ht="86.4">
-      <c r="B86" s="15">
-        <f>DATE(2026,10,17)</f>
-        <v>46312</v>
-      </c>
-      <c r="C86" s="5" t="s">
-        <v>326</v>
-      </c>
-      <c r="D86" s="7" t="s">
-        <v>10</v>
-      </c>
-      <c r="E86" s="5" t="s">
-        <v>394</v>
-      </c>
-      <c r="F86" s="5" t="s">
-        <v>395</v>
-      </c>
-      <c r="G86" s="5" t="s">
-        <v>396</v>
-      </c>
-      <c r="H86" s="5" t="s">
-        <v>397</v>
-      </c>
-      <c r="I86" s="5" t="s">
-        <v>398</v>
-      </c>
-    </row>
-    <row r="87" spans="2:9" ht="86.4">
-      <c r="B87" s="15">
-        <f>DATE(2026,10,17)</f>
-        <v>46312</v>
-      </c>
-      <c r="C87" s="5" t="s">
-        <v>326</v>
-      </c>
-      <c r="D87" s="7" t="s">
-        <v>10</v>
-      </c>
-      <c r="E87" s="5" t="s">
-        <v>399</v>
-      </c>
-      <c r="F87" s="5" t="s">
-        <v>400</v>
-      </c>
-      <c r="G87" s="5" t="s">
-        <v>401</v>
-      </c>
-      <c r="H87" s="21" t="s">
-        <v>449</v>
-      </c>
-      <c r="I87" s="21" t="s">
-        <v>450</v>
-      </c>
-    </row>
-    <row r="88" spans="2:9" ht="72">
-      <c r="B88" s="15">
-        <f>DATE(2026,10,17)</f>
-        <v>46312</v>
-      </c>
-      <c r="C88" s="5" t="s">
-        <v>9</v>
-      </c>
-      <c r="D88" s="7" t="s">
-        <v>10</v>
-      </c>
-      <c r="E88" s="5" t="s">
-        <v>403</v>
-      </c>
-      <c r="F88" s="5" t="s">
-        <v>404</v>
-      </c>
-      <c r="G88" s="5" t="s">
-        <v>405</v>
-      </c>
-      <c r="H88" s="5" t="s">
-        <v>406</v>
-      </c>
-      <c r="I88" s="5" t="s">
-        <v>407</v>
-      </c>
-    </row>
-    <row r="89" spans="2:9" ht="86.4">
-      <c r="B89" s="15">
-        <f>DATE(2026,10,17)</f>
-        <v>46312</v>
-      </c>
-      <c r="C89" s="5" t="s">
-        <v>9</v>
-      </c>
-      <c r="D89" s="7" t="s">
-        <v>10</v>
-      </c>
-      <c r="E89" s="5" t="s">
-        <v>408</v>
-      </c>
-      <c r="F89" s="5" t="s">
-        <v>409</v>
-      </c>
-      <c r="G89" s="5" t="s">
-        <v>410</v>
-      </c>
-      <c r="H89" s="5" t="s">
-        <v>411</v>
-      </c>
-      <c r="I89" s="5" t="s">
-        <v>412</v>
-      </c>
-    </row>
-    <row r="90" spans="2:9" ht="115.2">
-      <c r="B90" s="15">
-        <f>DATE(2026,10,17)</f>
-        <v>46312</v>
-      </c>
-      <c r="C90" s="5" t="s">
-        <v>9</v>
-      </c>
-      <c r="D90" s="7" t="s">
-        <v>10</v>
-      </c>
-      <c r="E90" s="5" t="s">
-        <v>413</v>
-      </c>
-      <c r="F90" s="5" t="s">
-        <v>414</v>
-      </c>
-      <c r="G90" s="5" t="s">
-        <v>415</v>
-      </c>
-      <c r="H90" s="5" t="s">
-        <v>416</v>
-      </c>
-      <c r="I90" s="5" t="s">
-        <v>417</v>
-      </c>
-    </row>
-    <row r="91" spans="2:9" ht="115.2">
-      <c r="B91" s="15">
-        <f>DATE(2026,10,17)</f>
-        <v>46312</v>
-      </c>
-      <c r="C91" s="5" t="s">
-        <v>9</v>
-      </c>
-      <c r="D91" s="7" t="s">
-        <v>10</v>
-      </c>
-      <c r="E91" s="5" t="s">
-        <v>418</v>
-      </c>
-      <c r="F91" s="5" t="s">
-        <v>419</v>
-      </c>
-      <c r="G91" s="5" t="s">
-        <v>420</v>
-      </c>
-      <c r="H91" s="5" t="s">
-        <v>421</v>
-      </c>
-      <c r="I91" s="5" t="s">
-        <v>422</v>
-      </c>
-    </row>
-    <row r="92" spans="2:9" ht="100.8">
-      <c r="B92" s="15">
-        <f>DATE(2026,10,17)</f>
-        <v>46312</v>
-      </c>
-      <c r="C92" s="5" t="s">
-        <v>9</v>
-      </c>
-      <c r="D92" s="7" t="s">
-        <v>10</v>
-      </c>
-      <c r="E92" s="5" t="s">
-        <v>423</v>
-      </c>
-      <c r="F92" s="5" t="s">
-        <v>424</v>
-      </c>
-      <c r="G92" s="5" t="s">
-        <v>425</v>
-      </c>
-      <c r="H92" s="5" t="s">
-        <v>426</v>
-      </c>
-      <c r="I92" s="5" t="s">
-        <v>427</v>
-      </c>
-    </row>
-    <row r="93" spans="2:9" ht="86.4">
-      <c r="B93" s="15">
-        <f>DATE(2026,10,17)</f>
-        <v>46312</v>
-      </c>
-      <c r="C93" s="5" t="s">
-        <v>9</v>
-      </c>
-      <c r="D93" s="7" t="s">
-        <v>10</v>
-      </c>
-      <c r="E93" s="5" t="s">
-        <v>428</v>
-      </c>
-      <c r="F93" s="5" t="s">
-        <v>429</v>
-      </c>
-      <c r="G93" s="5" t="s">
-        <v>430</v>
-      </c>
-      <c r="H93" s="5" t="s">
-        <v>431</v>
-      </c>
-      <c r="I93" s="5" t="s">
-        <v>432</v>
-      </c>
-    </row>
-    <row r="94" spans="2:9" ht="43.2">
-      <c r="B94" s="15">
-        <f>DATE(2026,10,17)</f>
-        <v>46312</v>
-      </c>
-      <c r="C94" s="5" t="s">
-        <v>9</v>
-      </c>
-      <c r="D94" s="7" t="s">
-        <v>10</v>
-      </c>
-      <c r="E94" s="5" t="s">
-        <v>433</v>
-      </c>
-      <c r="F94" s="5" t="s">
-        <v>434</v>
-      </c>
-      <c r="G94" s="5" t="s">
-        <v>435</v>
-      </c>
-      <c r="H94" s="5" t="s">
-        <v>436</v>
-      </c>
-      <c r="I94" s="5" t="s">
-        <v>437</v>
-      </c>
-    </row>
-    <row r="95" spans="2:9" ht="72">
-      <c r="B95" s="15">
-        <f>DATE(2026,10,17)</f>
-        <v>46312</v>
-      </c>
-      <c r="C95" s="5" t="s">
-        <v>9</v>
-      </c>
-      <c r="D95" s="7" t="s">
-        <v>10</v>
-      </c>
-      <c r="E95" s="5" t="s">
-        <v>438</v>
-      </c>
-      <c r="F95" s="5" t="s">
-        <v>439</v>
-      </c>
-      <c r="G95" s="5" t="s">
-        <v>440</v>
-      </c>
-      <c r="H95" s="5" t="s">
-        <v>441</v>
-      </c>
-      <c r="I95" s="5" t="s">
-        <v>442</v>
-      </c>
-    </row>
-    <row r="96" spans="2:9" ht="144">
-      <c r="B96" s="15">
-        <f>DATE(2026,10,17)</f>
-        <v>46312</v>
-      </c>
-      <c r="C96" s="5" t="s">
-        <v>9</v>
-      </c>
-      <c r="D96" s="7" t="s">
-        <v>10</v>
-      </c>
-      <c r="E96" s="5" t="s">
-        <v>443</v>
-      </c>
-      <c r="F96" s="5" t="s">
-        <v>444</v>
-      </c>
-      <c r="G96" s="5" t="s">
-        <v>445</v>
-      </c>
-      <c r="H96" s="5" t="s">
-        <v>446</v>
-      </c>
-      <c r="I96" s="5" t="s">
-        <v>447</v>
-      </c>
-    </row>
-    <row r="97" spans="2:9">
-      <c r="B97" s="8"/>
-      <c r="C97" s="5"/>
-      <c r="D97" s="7"/>
-      <c r="E97" s="5"/>
-      <c r="F97" s="5"/>
-      <c r="G97" s="5"/>
-      <c r="H97" s="5"/>
-      <c r="I97" s="5"/>
-    </row>
-    <row r="98" spans="2:9">
-      <c r="B98" s="8"/>
-      <c r="C98" s="5"/>
-      <c r="D98" s="7"/>
-      <c r="E98" s="5"/>
-      <c r="F98" s="5"/>
-      <c r="G98" s="5"/>
-      <c r="H98" s="5"/>
-      <c r="I98" s="5"/>
+      <c r="C98" s="5" t="s">
+        <v>67</v>
+      </c>
+      <c r="D98" s="7" t="s">
+        <v>10</v>
+      </c>
+      <c r="E98" s="5" t="s">
+        <v>456</v>
+      </c>
+      <c r="F98" s="5" t="s">
+        <v>457</v>
+      </c>
+      <c r="G98" s="5" t="s">
+        <v>458</v>
+      </c>
+      <c r="H98" s="5" t="s">
+        <v>459</v>
+      </c>
+      <c r="I98" s="5" t="s">
+        <v>460</v>
+      </c>
     </row>
     <row r="99" spans="2:9">
       <c r="B99" s="8"/>

--- a/docs/AI-Usage/AI Usage Register/AI Usage Register v0.15.xlsx
+++ b/docs/AI-Usage/AI Usage Register/AI Usage Register v0.15.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\elind\m4-wt\records\docs\AI-Usage\AI Usage Register\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7746990F-0A8D-440F-9984-5274705A429E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8ECADAEB-97D1-488F-B48C-FE7850621D34}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-96" yWindow="-96" windowWidth="30912" windowHeight="17472" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="30936" windowHeight="17496" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="AI Usage Register" sheetId="1" r:id="rId1"/>
@@ -1283,39 +1283,21 @@
     <t>Reviewing PR #122 (TD-008 integration job) and PR #123 (DEF-019, TD-007, README, .gitignore)</t>
   </si>
   <si>
-    <t>I checked the TAP summary and the failing-check names against `docs/evidence/M3_API_Test_Run.txt`, confirmed the ruleset's required checks, and read the reviews before they were posted</t>
-  </si>
-  <si>
     <t>Accepted with changes: #123's description was corrected to four commits and to mention the secret-scan fix before I approved</t>
   </si>
   <si>
-    <t>#122's description stops mid-sentence and lacks the template's sections; this was flagged in the review, not fixed for the author</t>
-  </si>
-  <si>
-    <t>Staging Nginx site file and systemd unit in `deploy/` (PR #133)</t>
-  </si>
-  <si>
     <t>Wrote both files and the README from the deploy record and the 15/10 note, marked every line the record does not show as NOT RECORDED, and checked them for IPs and secrets</t>
   </si>
   <si>
-    <t>I checked each recorded line against the deploy record. Comparing with the VM (`diff -u` against the live files) is my step before merge, and is not yet done</t>
-  </si>
-  <si>
     <t>Accepted with changes: HSTS left out, because browsers ignore it for an IP host (RFC 6797 §8.1)</t>
   </si>
   <si>
-    <t>The live files were never captured at M3, so the repository files are reconstructions until the VM comparison is posted on the PR. The first draft's HSTS comment gave the wrong reason and was corrected</t>
-  </si>
-  <si>
     <t>DEC-003 v0.5 and Decision Log v0.10 (PR #134)</t>
   </si>
   <si>
     <t>Drafted the v0.5 text closing the eight M3 follow-ups and the extra ones (access-list exception, environment file owner, Test row, staging subdomain), and the final-status and consequence cells for all 19 decisions. Wrote the Decision Log through Excel itself, not a script library</t>
   </si>
   <si>
-    <t>I checked each statement against the deploy record, PED v3.0 M3.3 and M3.8, and `gh repo view` (repository public). A line comparison shows every v0.4 line kept; a cell comparison shows only B2 and L4:M23 changed</t>
-  </si>
-  <si>
     <t>Four Decision Log cells wait for the Sunday RC evidence ([Sunday RC check]), so the PR is a draft</t>
   </si>
   <si>
@@ -1343,9 +1325,6 @@
     <t>I checked every cited ID and figure against the repository; the statements that depend on Sunday are marked and not asserted</t>
   </si>
   <si>
-    <t>Read both diffs and the CI logs. For #122, extracted the TAP summary (40 / 25 / 15 / 0 skipped) and matched the 15 failing checks to the M3 run file. For #123, ran the suite in a clean worktree, checked that the two .gitleaksignore` entries are the `openapi.yaml` SHA-256 lines and that the hash matches the file on dev, and drafted the review comments</t>
-  </si>
-  <si>
     <t>M4 preparation: strict scope table and build plan</t>
   </si>
   <si>
@@ -1481,9 +1460,6 @@
     <t>The guard first failed as a .js file in an ES-module repository and mis-read backslashes in Windows paths; both were fixed and re-tested. The AI put PR reviews into the preparation prompt before the project was fully understood (removed), wrote an unclear teammate message (rewritten), and wrongly said the FR-3.5 status chips should be mapped (corrected: the chips show all seven statuses).</t>
   </si>
   <si>
-    <t>Accepted with changes: the production position on exposing the commit hash on /health (item 4) is my decision, not the draft’s; the other 18 decision texts were accepted after checking each against the deploy record.</t>
-  </si>
-  <si>
     <t>Accepted with changes: the no-go decision and the reflection are the team’s own; the drafts were revised before use (14 listed corrections) to match the final scope figure and current defect statuses, and staging-dependent statements stay marked until Sunday’s RC evidence.</t>
   </si>
   <si>
@@ -1505,9 +1481,6 @@
     <t>TD Register v0.3 planned the known failures as expected failures. node:test has no expected-failure mode that fails when the test starts passing, so I made the job non-required instead of changing any assertion. MongoDB could not be downloaded in the drafting environment, so the replica set was first tried in CI itself</t>
   </si>
   <si>
-    <t>Pre-RC fixes : TD-007 OpenAPI tests parse the YAML, DEF-019 test titles, scripts README, .gitignore</t>
-  </si>
-  <si>
     <t>Rewrote the two OpenAPI contract tests to parse the file with the yaml package as a dev dependency, and added a test for valid YAML, OpenAPI 3.x and resolving references. Corrected the two DEF-019 titles, the stale staging-marker line in the scripts README, and added ignores for the perf fixture file and staging.crt</t>
   </si>
   <si>
@@ -1518,6 +1491,33 @@
   </si>
   <si>
     <t>The negative verification ran in a scratch copy, not in my checkout, and the evidence file says so. One commit message was joined to old text by mistake and was amended before review</t>
+  </si>
+  <si>
+    <t>Pre-RC fixes: TD-007 OpenAPI tests parse the YAML, DEF-019 test titles, scripts README, .gitignore</t>
+  </si>
+  <si>
+    <t>Staging Nginx site file and systemd unit in deploy/ (PR #133)</t>
+  </si>
+  <si>
+    <t>Read both diffs and the CI logs. For #122, extracted the TAP summary (40 / 25 / 15 / 0 skipped) and matched the 15 failing checks to the M3 run file. For #123, ran the suite in a clean worktree, checked that the two .gitleaksignore entries are the openapi.yaml SHA-256 lines and that the hash matches the file on dev, and drafted the review comments</t>
+  </si>
+  <si>
+    <t>I checked the TAP summary and the failing-check names against docs/evidence/M3_API_Test_Run.txt, confirmed the ruleset's required checks, and read the reviews before they were posted</t>
+  </si>
+  <si>
+    <t>I checked each recorded line against the deploy record. Comparing with the VM (diff -u against the live files) is my step before merge, and is not yet done</t>
+  </si>
+  <si>
+    <t>I checked each statement against the deploy record, PED v3.0 M3.3 and M3.8, and gh repo view (repository public). A line comparison shows every v0.4 line kept; a cell comparison shows only B2 and L4:M23 changed</t>
+  </si>
+  <si>
+    <t>Accepted with changes: I confirmed the /health commit-hash position as my decision (accepted for staging, to verify the deployed release; not accepted as-is for production, because the repository is public and the hash on an unauthenticated endpoint reveals the exact source and patch level).</t>
+  </si>
+  <si>
+    <t>#122's description stopped mid-sentence and lacked the template's sections. Because C. Burger was unavailable, I completed it on 17/10/2026 from his commit and the CI run, with a note in the description saying so.</t>
+  </si>
+  <si>
+    <t>The live files were never captured at M3, so the repository files are reconstructions until the VM comparison is posted on the PR. The first draft's HSTS comment gave the wrong reason and was corrected The comparison was run by E. Lindsay on 17/10/2026, 22:57 UTC (PR #133).</t>
   </si>
 </sst>
 </file>
@@ -4243,19 +4243,19 @@
         <v>381</v>
       </c>
       <c r="F83" s="5" t="s">
-        <v>402</v>
+        <v>454</v>
       </c>
       <c r="G83" s="5" t="s">
+        <v>455</v>
+      </c>
+      <c r="H83" s="5" t="s">
         <v>382</v>
       </c>
-      <c r="H83" s="5" t="s">
-        <v>383</v>
-      </c>
       <c r="I83" s="5" t="s">
-        <v>384</v>
-      </c>
-    </row>
-    <row r="84" spans="2:9" ht="72">
+        <v>459</v>
+      </c>
+    </row>
+    <row r="84" spans="2:9" ht="86.4">
       <c r="B84" s="15">
         <f t="shared" si="3"/>
         <v>46312</v>
@@ -4267,19 +4267,19 @@
         <v>10</v>
       </c>
       <c r="E84" s="5" t="s">
-        <v>385</v>
+        <v>453</v>
       </c>
       <c r="F84" s="5" t="s">
-        <v>386</v>
+        <v>383</v>
       </c>
       <c r="G84" s="5" t="s">
-        <v>387</v>
+        <v>456</v>
       </c>
       <c r="H84" s="5" t="s">
-        <v>388</v>
+        <v>384</v>
       </c>
       <c r="I84" s="5" t="s">
-        <v>389</v>
+        <v>460</v>
       </c>
     </row>
     <row r="85" spans="2:9" ht="100.8">
@@ -4294,19 +4294,19 @@
         <v>10</v>
       </c>
       <c r="E85" s="5" t="s">
-        <v>390</v>
+        <v>385</v>
       </c>
       <c r="F85" s="5" t="s">
-        <v>391</v>
+        <v>386</v>
       </c>
       <c r="G85" s="5" t="s">
-        <v>392</v>
+        <v>457</v>
       </c>
       <c r="H85" s="5" t="s">
-        <v>448</v>
+        <v>458</v>
       </c>
       <c r="I85" s="5" t="s">
-        <v>393</v>
+        <v>387</v>
       </c>
     </row>
     <row r="86" spans="2:9" ht="86.4">
@@ -4321,19 +4321,19 @@
         <v>10</v>
       </c>
       <c r="E86" s="5" t="s">
-        <v>394</v>
+        <v>388</v>
       </c>
       <c r="F86" s="5" t="s">
-        <v>395</v>
+        <v>389</v>
       </c>
       <c r="G86" s="5" t="s">
-        <v>396</v>
+        <v>390</v>
       </c>
       <c r="H86" s="5" t="s">
-        <v>397</v>
+        <v>391</v>
       </c>
       <c r="I86" s="5" t="s">
-        <v>398</v>
+        <v>392</v>
       </c>
     </row>
     <row r="87" spans="2:9" ht="86.4">
@@ -4348,19 +4348,19 @@
         <v>10</v>
       </c>
       <c r="E87" s="5" t="s">
-        <v>399</v>
+        <v>393</v>
       </c>
       <c r="F87" s="5" t="s">
-        <v>400</v>
+        <v>394</v>
       </c>
       <c r="G87" s="5" t="s">
-        <v>401</v>
+        <v>395</v>
       </c>
       <c r="H87" s="5" t="s">
-        <v>449</v>
+        <v>441</v>
       </c>
       <c r="I87" s="5" t="s">
-        <v>450</v>
+        <v>442</v>
       </c>
     </row>
     <row r="88" spans="2:9" ht="72">
@@ -4375,19 +4375,19 @@
         <v>10</v>
       </c>
       <c r="E88" s="5" t="s">
-        <v>403</v>
+        <v>396</v>
       </c>
       <c r="F88" s="5" t="s">
-        <v>404</v>
+        <v>397</v>
       </c>
       <c r="G88" s="5" t="s">
-        <v>405</v>
+        <v>398</v>
       </c>
       <c r="H88" s="5" t="s">
-        <v>406</v>
+        <v>399</v>
       </c>
       <c r="I88" s="5" t="s">
-        <v>407</v>
+        <v>400</v>
       </c>
     </row>
     <row r="89" spans="2:9" ht="86.4">
@@ -4402,19 +4402,19 @@
         <v>10</v>
       </c>
       <c r="E89" s="5" t="s">
-        <v>408</v>
+        <v>401</v>
       </c>
       <c r="F89" s="5" t="s">
-        <v>409</v>
+        <v>402</v>
       </c>
       <c r="G89" s="5" t="s">
-        <v>410</v>
+        <v>403</v>
       </c>
       <c r="H89" s="5" t="s">
-        <v>411</v>
+        <v>404</v>
       </c>
       <c r="I89" s="5" t="s">
-        <v>412</v>
+        <v>405</v>
       </c>
     </row>
     <row r="90" spans="2:9" ht="115.2">
@@ -4429,19 +4429,19 @@
         <v>10</v>
       </c>
       <c r="E90" s="5" t="s">
-        <v>413</v>
+        <v>406</v>
       </c>
       <c r="F90" s="5" t="s">
-        <v>414</v>
+        <v>407</v>
       </c>
       <c r="G90" s="5" t="s">
-        <v>415</v>
+        <v>408</v>
       </c>
       <c r="H90" s="5" t="s">
-        <v>416</v>
+        <v>409</v>
       </c>
       <c r="I90" s="5" t="s">
-        <v>417</v>
+        <v>410</v>
       </c>
     </row>
     <row r="91" spans="2:9" ht="115.2">
@@ -4456,19 +4456,19 @@
         <v>10</v>
       </c>
       <c r="E91" s="5" t="s">
-        <v>418</v>
+        <v>411</v>
       </c>
       <c r="F91" s="5" t="s">
-        <v>419</v>
+        <v>412</v>
       </c>
       <c r="G91" s="5" t="s">
-        <v>420</v>
+        <v>413</v>
       </c>
       <c r="H91" s="5" t="s">
-        <v>421</v>
+        <v>414</v>
       </c>
       <c r="I91" s="5" t="s">
-        <v>422</v>
+        <v>415</v>
       </c>
     </row>
     <row r="92" spans="2:9" ht="100.8">
@@ -4483,19 +4483,19 @@
         <v>10</v>
       </c>
       <c r="E92" s="5" t="s">
-        <v>423</v>
+        <v>416</v>
       </c>
       <c r="F92" s="5" t="s">
-        <v>424</v>
+        <v>417</v>
       </c>
       <c r="G92" s="5" t="s">
-        <v>425</v>
+        <v>418</v>
       </c>
       <c r="H92" s="5" t="s">
-        <v>426</v>
+        <v>419</v>
       </c>
       <c r="I92" s="5" t="s">
-        <v>427</v>
+        <v>420</v>
       </c>
     </row>
     <row r="93" spans="2:9" ht="86.4">
@@ -4510,19 +4510,19 @@
         <v>10</v>
       </c>
       <c r="E93" s="5" t="s">
-        <v>428</v>
+        <v>421</v>
       </c>
       <c r="F93" s="5" t="s">
-        <v>429</v>
+        <v>422</v>
       </c>
       <c r="G93" s="5" t="s">
-        <v>430</v>
+        <v>423</v>
       </c>
       <c r="H93" s="5" t="s">
-        <v>431</v>
+        <v>424</v>
       </c>
       <c r="I93" s="5" t="s">
-        <v>432</v>
+        <v>425</v>
       </c>
     </row>
     <row r="94" spans="2:9" ht="43.2">
@@ -4537,19 +4537,19 @@
         <v>10</v>
       </c>
       <c r="E94" s="5" t="s">
-        <v>433</v>
+        <v>426</v>
       </c>
       <c r="F94" s="5" t="s">
-        <v>434</v>
+        <v>427</v>
       </c>
       <c r="G94" s="5" t="s">
-        <v>435</v>
+        <v>428</v>
       </c>
       <c r="H94" s="5" t="s">
-        <v>436</v>
+        <v>429</v>
       </c>
       <c r="I94" s="5" t="s">
-        <v>437</v>
+        <v>430</v>
       </c>
     </row>
     <row r="95" spans="2:9" ht="72">
@@ -4564,19 +4564,19 @@
         <v>10</v>
       </c>
       <c r="E95" s="5" t="s">
-        <v>438</v>
+        <v>431</v>
       </c>
       <c r="F95" s="5" t="s">
-        <v>439</v>
+        <v>432</v>
       </c>
       <c r="G95" s="5" t="s">
-        <v>440</v>
+        <v>433</v>
       </c>
       <c r="H95" s="5" t="s">
-        <v>441</v>
+        <v>434</v>
       </c>
       <c r="I95" s="5" t="s">
-        <v>442</v>
+        <v>435</v>
       </c>
     </row>
     <row r="96" spans="2:9" ht="144">
@@ -4591,19 +4591,19 @@
         <v>10</v>
       </c>
       <c r="E96" s="5" t="s">
-        <v>443</v>
+        <v>436</v>
       </c>
       <c r="F96" s="5" t="s">
-        <v>444</v>
+        <v>437</v>
       </c>
       <c r="G96" s="5" t="s">
-        <v>445</v>
+        <v>438</v>
       </c>
       <c r="H96" s="5" t="s">
-        <v>446</v>
+        <v>439</v>
       </c>
       <c r="I96" s="5" t="s">
-        <v>447</v>
+        <v>440</v>
       </c>
     </row>
     <row r="97" spans="2:9" ht="115.2">
@@ -4618,19 +4618,19 @@
         <v>10</v>
       </c>
       <c r="E97" s="5" t="s">
-        <v>451</v>
+        <v>443</v>
       </c>
       <c r="F97" s="5" t="s">
-        <v>452</v>
+        <v>444</v>
       </c>
       <c r="G97" s="5" t="s">
-        <v>453</v>
+        <v>445</v>
       </c>
       <c r="H97" s="5" t="s">
-        <v>454</v>
+        <v>446</v>
       </c>
       <c r="I97" s="5" t="s">
-        <v>455</v>
+        <v>447</v>
       </c>
     </row>
     <row r="98" spans="2:9" ht="115.2">
@@ -4645,19 +4645,19 @@
         <v>10</v>
       </c>
       <c r="E98" s="5" t="s">
-        <v>456</v>
+        <v>452</v>
       </c>
       <c r="F98" s="5" t="s">
-        <v>457</v>
+        <v>448</v>
       </c>
       <c r="G98" s="5" t="s">
-        <v>458</v>
+        <v>449</v>
       </c>
       <c r="H98" s="5" t="s">
-        <v>459</v>
+        <v>450</v>
       </c>
       <c r="I98" s="5" t="s">
-        <v>460</v>
+        <v>451</v>
       </c>
     </row>
     <row r="99" spans="2:9">
